--- a/out/Attention-mamba2_repeat_5_000007.xlsx
+++ b/out/Attention-mamba2_repeat_5_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.103542575915647</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.103542575915647</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.103542575915647</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000205750943202409</v>
+        <v>-6.038105188275221e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.372004500461972</v>
+        <v>0.6961042754547568</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.74767569180898</v>
+        <v>1.393284754049746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3556926558241119</v>
+        <v>0.1043839412694196</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.083872946686411</v>
+        <v>0.9050139873536248</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4447315546856952</v>
+        <v>0.1305139476654237</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.617699886707992</v>
+        <v>1.061674472939382</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6375204118713611</v>
+        <v>0.1870911250288232</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.448260463069589</v>
+        <v>1.305416430128927</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6820205607962044</v>
+        <v>0.2001504448110093</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.174829076493504</v>
+        <v>1.518640143900103</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7228043268331424</v>
+        <v>0.2121183915624241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.938469558396712</v>
+        <v>1.742743104207468</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3261888152876714</v>
+        <v>0.09572575083263495</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.867440737895589</v>
+        <v>1.721898468050247</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1575336456588991</v>
+        <v>0.04623051919669491</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.856064724623955</v>
+        <v>1.71855998084306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07506009208127945</v>
+        <v>0.02202746602705347</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.84852609894795</v>
+        <v>1.716347619634103</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02223978170443824</v>
+        <v>0.006523580880987169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.817865116941003</v>
+        <v>1.707346355452162</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01471074712324716</v>
+        <v>0.004313887701662389</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.825035010032151</v>
+        <v>1.709447096823808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007526192468847799</v>
+        <v>0.002204963193759101</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.825368880462292</v>
+        <v>1.709541551479308</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003847496000060362</v>
+        <v>0.001125481580367856</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.825533222639508</v>
+        <v>1.709586259537464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001443677731488236</v>
+        <v>0.0004203693234568383</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.824569156000923</v>
+        <v>1.70929965271882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007845307202364825</v>
+        <v>0.0002268266796096673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.824693732692013</v>
+        <v>1.709332699793215</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000374880916366881</v>
+        <v>0.000106262193078166</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.824659259781214</v>
+        <v>1.709319046125635</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002301652730669746</v>
+        <v>6.387685822045283e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.824744721227228</v>
+        <v>1.70934067507415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001185242988982542</v>
+        <v>3.10279205119908e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.824750483392241</v>
+        <v>1.709338859507548</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.494558784711067e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.824741772936765</v>
+        <v>1.709332746370905</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.337439133288135e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.82475354974197</v>
+        <v>1.709332779412467</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.824745118354042</v>
+        <v>1.70932675070418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.824738063499462</v>
+        <v>1.709321066170152</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.824733724962188</v>
+        <v>1.709316314894938</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.824728146667064</v>
+        <v>1.709311025747376</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.824723100045997</v>
+        <v>1.709311003013075</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.824723418326213</v>
+        <v>1.709311321293292</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.82472450957267</v>
+        <v>1.709312412539749</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.824723819965534</v>
+        <v>1.709311722932613</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.824723850277936</v>
+        <v>1.709311753245014</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.824723660825426</v>
+        <v>1.709311563792504</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.824723713872129</v>
+        <v>1.709311616839207</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.824723766918831</v>
+        <v>1.70931166988591</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.824723729028329</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.824723600200622</v>
+        <v>1.709311503167702</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.824723456216716</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.824723297076607</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.82472335012331</v>
+        <v>1.709311253090388</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.824723297076607</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.824723297076607</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.824723115202198</v>
+        <v>1.709311018169276</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.824723281920406</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.824723478951016</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.824723319810908</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.824723357701409</v>
+        <v>1.709311260668489</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.82472355473202</v>
+        <v>1.709311457699099</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.824723531997718</v>
+        <v>1.709311434964798</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.824723380435711</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.824723304654707</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.824723403170013</v>
+        <v>1.709311306137091</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.824723410748113</v>
+        <v>1.709311313715192</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.824723675981627</v>
+        <v>1.709311578948705</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.824723380435711</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.824723622934924</v>
+        <v>1.709311525902003</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.824723706294028</v>
+        <v>1.709311609261107</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.82472353957582</v>
+        <v>1.709311442542898</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.824723729028329</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.824723380435711</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.824723175827001</v>
+        <v>1.709311078794079</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.824723289498506</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.824723304654707</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.824723069733595</v>
+        <v>1.709310972700674</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.824723130358398</v>
+        <v>1.709311033325477</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.824723001530691</v>
+        <v>1.70931090449777</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.824723137936499</v>
+        <v>1.709311040903577</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.824723312232807</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.824723456216716</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.824723289498506</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.824723281920406</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.824722993952591</v>
+        <v>1.70931089691967</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.824723009108792</v>
+        <v>1.709310912075871</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.824723236451804</v>
+        <v>1.709311139418882</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.824723221295603</v>
+        <v>1.709311124262682</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.824723327389008</v>
+        <v>1.709311230356087</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.824723054577395</v>
+        <v>1.709310957544473</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.824723153092699</v>
+        <v>1.709311056059778</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.824723304654707</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.824723319810908</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.824723297076607</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.824723380435711</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.824723478951016</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.824723312232807</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.824723297076607</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.824723266764205</v>
+        <v>1.709311169731284</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.824723251608005</v>
+        <v>1.709311154575083</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.824723289498506</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.824723304654707</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.824723297076607</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000007.xlsx
+++ b/out/Attention-mamba2_repeat_5_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.4160766030030931</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.000205750943202409</v>
+        <v>-0.0001186498147072271</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.372004500461972</v>
+        <v>1.367857129031888</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC40" t="n">
-        <v>4.74767569180898</v>
+        <v>2.737828718329798</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.3556926558241119</v>
+        <v>0.2051162782020604</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.083872946686411</v>
+        <v>1.778368293286133</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.4447315546856952</v>
+        <v>0.2564620882733506</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC42" t="n">
-        <v>3.617699886707992</v>
+        <v>2.086208765526209</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.6375204118713611</v>
+        <v>0.3676371872936156</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC43" t="n">
-        <v>4.448260463069589</v>
+        <v>2.565165784747723</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.6820205607962044</v>
+        <v>0.3932986208492458</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.174829076493504</v>
+        <v>2.984153946172949</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.7228043268331424</v>
+        <v>0.4168180028382902</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.416076603003093</v>
       </c>
       <c r="JC45" t="n">
-        <v>5.938469558396712</v>
+        <v>3.424520395835764</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3261888152876714</v>
+        <v>0.188102212376806</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC46" t="n">
-        <v>5.867440737895589</v>
+        <v>3.383560443646744</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1575336456588991</v>
+        <v>0.09084412791397287</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC47" t="n">
-        <v>5.856064724623955</v>
+        <v>3.377000276561446</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.07506009208127945</v>
+        <v>0.04328513524470294</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC48" t="n">
-        <v>5.84852609894795</v>
+        <v>3.372652988958348</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02223978170443824</v>
+        <v>0.01282400657036277</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC49" t="n">
-        <v>5.817865116941003</v>
+        <v>3.354970837075625</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01471074712324716</v>
+        <v>0.008480898203934023</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC50" t="n">
-        <v>5.825035010032151</v>
+        <v>3.359103269710588</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.007526192468847799</v>
+        <v>0.004338177888358268</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC51" t="n">
-        <v>5.825368880462292</v>
+        <v>3.359293680440851</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.003847496000060362</v>
+        <v>0.002216703337374763</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC52" t="n">
-        <v>5.825533222639508</v>
+        <v>3.359386325596459</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001443677731488236</v>
+        <v>0.0008298440636528337</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC53" t="n">
-        <v>5.824569156000923</v>
+        <v>3.358828384556576</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0007845307202364825</v>
+        <v>0.0004504032994467486</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC54" t="n">
-        <v>5.824693732692013</v>
+        <v>3.358898124716954</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000374880916366881</v>
+        <v>0.0002143454663540987</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC55" t="n">
-        <v>5.824659259781214</v>
+        <v>3.358876124388172</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002301652730669746</v>
+        <v>0.0001307858062060355</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC56" t="n">
-        <v>5.824744721227228</v>
+        <v>3.358923247966011</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001185242988982542</v>
+        <v>6.602647186649616e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC57" t="n">
-        <v>5.824750483392241</v>
+        <v>3.358924436210893</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.494558784711067e-05</v>
+        <v>2.896916644669604e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC58" t="n">
-        <v>5.824741772936765</v>
+        <v>3.358917303307055</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.337439133288135e-05</v>
+        <v>1.67454884219661e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC59" t="n">
-        <v>5.82475354974197</v>
+        <v>3.358922090553054</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.248416916455026e-05</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC60" t="n">
-        <v>5.824745118354042</v>
+        <v>3.358915031720298</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>2.205584102398162e-06</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC61" t="n">
-        <v>5.824738063499462</v>
+        <v>3.358908799058048</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.386750013692762</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC62" t="n">
-        <v>5.824733724962188</v>
+        <v>3.358904213148516</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC63" t="n">
-        <v>5.824728146667064</v>
+        <v>3.358898780017047</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC64" t="n">
-        <v>5.824723100045997</v>
+        <v>3.35889373339598</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030931</v>
       </c>
       <c r="JC65" t="n">
-        <v>5.824723418326213</v>
+        <v>3.358894051676196</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC66" t="n">
-        <v>5.82472450957267</v>
+        <v>3.358895142922653</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC67" t="n">
-        <v>5.824723819965534</v>
+        <v>3.358894453315517</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC68" t="n">
-        <v>5.824723850277936</v>
+        <v>3.358894483627919</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030931</v>
       </c>
       <c r="JC69" t="n">
-        <v>5.824723660825426</v>
+        <v>3.358894294175409</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311462</v>
       </c>
       <c r="JC70" t="n">
-        <v>5.824723713872129</v>
+        <v>3.358894347222112</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC71" t="n">
-        <v>5.824723766918831</v>
+        <v>3.358894400268814</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC72" t="n">
-        <v>5.824723729028329</v>
+        <v>3.358894362378312</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC73" t="n">
-        <v>5.824723600200622</v>
+        <v>3.358894233550605</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC74" t="n">
-        <v>5.824723456216716</v>
+        <v>3.358894089566698</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC75" t="n">
-        <v>5.824723297076607</v>
+        <v>3.35889393042659</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC76" t="n">
-        <v>5.82472335012331</v>
+        <v>3.358893983473293</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC77" t="n">
-        <v>5.824723297076607</v>
+        <v>3.35889393042659</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC78" t="n">
-        <v>5.824723297076607</v>
+        <v>3.35889393042659</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC79" t="n">
-        <v>5.824723115202198</v>
+        <v>3.358893748552181</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC80" t="n">
-        <v>5.824723281920406</v>
+        <v>3.358893915270389</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC81" t="n">
-        <v>5.824723478951016</v>
+        <v>3.358894112300999</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC82" t="n">
-        <v>5.824723319810908</v>
+        <v>3.358893953160891</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC83" t="n">
-        <v>5.824723357701409</v>
+        <v>3.358893991051393</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC84" t="n">
-        <v>5.82472355473202</v>
+        <v>3.358894188082003</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC85" t="n">
-        <v>5.824723531997718</v>
+        <v>3.358894165347702</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC86" t="n">
-        <v>5.824723380435711</v>
+        <v>3.358894013785694</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC87" t="n">
-        <v>5.824723304654707</v>
+        <v>3.35889393800469</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC88" t="n">
-        <v>5.824723403170013</v>
+        <v>3.358894036519996</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC89" t="n">
-        <v>5.824723410748113</v>
+        <v>3.358894044098096</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC90" t="n">
-        <v>5.824723675981627</v>
+        <v>3.35889430933161</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC91" t="n">
-        <v>5.824723380435711</v>
+        <v>3.358894013785694</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC92" t="n">
-        <v>5.824723622934924</v>
+        <v>3.358894256284906</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC93" t="n">
-        <v>5.824723706294028</v>
+        <v>3.358894339644011</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC94" t="n">
-        <v>5.82472353957582</v>
+        <v>3.358894172925803</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC95" t="n">
-        <v>5.824723729028329</v>
+        <v>3.358894362378312</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC96" t="n">
-        <v>5.824723380435711</v>
+        <v>3.358894013785694</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC97" t="n">
-        <v>5.824723175827001</v>
+        <v>3.358893809176983</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC98" t="n">
-        <v>5.824723289498506</v>
+        <v>3.358893922848489</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC99" t="n">
-        <v>5.824723304654707</v>
+        <v>3.35889393800469</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC100" t="n">
-        <v>5.824723069733595</v>
+        <v>3.358893703083579</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC101" t="n">
-        <v>5.824723130358398</v>
+        <v>3.358893763708381</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC102" t="n">
-        <v>5.824723001530691</v>
+        <v>3.358893634880674</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC103" t="n">
-        <v>5.824723137936499</v>
+        <v>3.358893771286482</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC104" t="n">
-        <v>5.824723312232807</v>
+        <v>3.35889394558279</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC105" t="n">
-        <v>5.824723456216716</v>
+        <v>3.358894089566698</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC106" t="n">
-        <v>5.824723289498506</v>
+        <v>3.358893922848489</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC107" t="n">
-        <v>5.824723281920406</v>
+        <v>3.358893915270389</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC108" t="n">
-        <v>5.824722993952591</v>
+        <v>3.358893627302574</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC109" t="n">
-        <v>5.824723009108792</v>
+        <v>3.358893642458775</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC110" t="n">
-        <v>5.824723236451804</v>
+        <v>3.358893869801787</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC111" t="n">
-        <v>5.824723221295603</v>
+        <v>3.358893854645586</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC112" t="n">
-        <v>5.824723327389008</v>
+        <v>3.358893960738992</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC113" t="n">
-        <v>5.824723054577395</v>
+        <v>3.358893687927377</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC114" t="n">
-        <v>5.824723153092699</v>
+        <v>3.358893786442682</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC115" t="n">
-        <v>5.824723304654707</v>
+        <v>3.35889393800469</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC116" t="n">
-        <v>5.824723319810908</v>
+        <v>3.358893953160891</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC117" t="n">
-        <v>5.824723297076607</v>
+        <v>3.35889393042659</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC118" t="n">
-        <v>5.824723380435711</v>
+        <v>3.358894013785694</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC119" t="n">
-        <v>5.824723478951016</v>
+        <v>3.358894112300999</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC120" t="n">
-        <v>5.824723312232807</v>
+        <v>3.35889394558279</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC121" t="n">
-        <v>5.824723297076607</v>
+        <v>3.35889393042659</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC122" t="n">
-        <v>5.824723266764205</v>
+        <v>3.358893900114188</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC123" t="n">
-        <v>5.824723251608005</v>
+        <v>3.358893884957988</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC124" t="n">
-        <v>5.824723289498506</v>
+        <v>3.358893922848489</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC125" t="n">
-        <v>5.824723304654707</v>
+        <v>3.35889393800469</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC126" t="n">
-        <v>5.824723297076607</v>
+        <v>3.35889393042659</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000007.xlsx
+++ b/out/Attention-mamba2_repeat_5_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2022098004817963</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1644747257232666</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1431114673614502</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.2115134596824646</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.2847812175750732</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.2380796074867249</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.2111549079418182</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2362108528614044</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2208275198936462</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.2269338369369507</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.2165277302265167</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.2107262015342712</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.2270304560661316</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2268794178962708</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.2436006665229797</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.2202641367912292</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2206695973873138</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.2150301933288574</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.2331482172012329</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.2258205711841583</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.2503321468830109</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2713155448436737</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.25316521525383</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2328386902809143</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2221862375736237</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2179197072982788</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2128949761390686</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.2417771816253662</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2391280233860016</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2300002872943878</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.2148258090019226</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2269738018512726</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.2244530618190765</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.2349183559417725</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3079775273799896</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.09377837926149368</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0452384427189827</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4160766030030931</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0128650888800621</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.2445617031931146</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001186498147072271</v>
+        <v>-0.0001762581139509566</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.367857129031888</v>
+        <v>2.031995661651695</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01095288991928101</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.737828718329798</v>
+        <v>4.067132573440041</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2051162782020604</v>
+        <v>0.304706836431729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02926206588745117</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.778368293286133</v>
+        <v>2.641823215454815</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2564620882733506</v>
+        <v>0.3809826339917982</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03131918609142303</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.086208765526209</v>
+        <v>3.099130150153705</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3676371872936156</v>
+        <v>0.5461367990545677</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.05926530435681343</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.565165784747723</v>
+        <v>3.810636331820818</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.3932986208492458</v>
+        <v>0.5842581963286199</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.009758524596691132</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.984153946172949</v>
+        <v>4.43305701572845</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4168180028382902</v>
+        <v>0.619196663161341</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.02585101127624512</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.416076603003093</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.424520395835764</v>
+        <v>5.087235660467096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.188102212376806</v>
+        <v>0.2794319377854967</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.03266854584217072</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.383560443646744</v>
+        <v>5.026388322909726</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.09084412791397287</v>
+        <v>0.1349522109205024</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0105474665760994</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.377000276561446</v>
+        <v>5.016642981444461</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04328513524470294</v>
+        <v>0.06430132361609035</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01222645491361618</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.372652988958348</v>
+        <v>5.010184959644628</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01282400657036277</v>
+        <v>0.01905167046229239</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.002193674445152283</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.354970837075625</v>
+        <v>4.983919210836554</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008480898203934023</v>
+        <v>0.01260080754943257</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.02357619628310204</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.359103269710588</v>
+        <v>4.990060604748933</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004338177888358268</v>
+        <v>0.00644679370502156</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.08561885356903076</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.359293680440851</v>
+        <v>4.990345910255853</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002216703337374763</v>
+        <v>0.003295845148732146</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.05944843590259552</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.359386325596459</v>
+        <v>4.990485984322567</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008298440636528337</v>
+        <v>0.001235534379262914</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.05609896406531334</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.358828384556576</v>
+        <v>4.9896594645375</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004504032994467486</v>
+        <v>0.0006715049013520539</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.08212609589099884</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.358898124716954</v>
+        <v>4.989765491587336</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002143454663540987</v>
+        <v>0.0003208392797289147</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.08625451475381851</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.358876124388172</v>
+        <v>4.98973523747574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001307858062060355</v>
+        <v>0.0001967107990741833</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.07147236913442612</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.358923247966011</v>
+        <v>4.989807667428328</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.602647186649616e-05</v>
+        <v>9.999565406351607e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.106353834271431</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.358924436210893</v>
+        <v>4.98981186073719</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.896916644669604e-05</v>
+        <v>4.595374967004406e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02984552830457687</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.358917303307055</v>
+        <v>4.989803676537635</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.67454884219661e-05</v>
+        <v>2.82578058218305e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.04234930872917175</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.358922090553054</v>
+        <v>4.989813216435479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>5.490501498730158e-06</v>
+        <v>1.015294660927689e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.05573703348636627</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.358915031720298</v>
+        <v>4.989805242565942</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.07937610149383545</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.358908799058048</v>
+        <v>4.989798461775472</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.06973107159137726</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.358904213148516</v>
+        <v>4.989794041231621</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.07617244124412537</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.358898780017047</v>
+        <v>4.989788462936497</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.05462924018502235</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.35889373339598</v>
+        <v>4.98978341631543</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02949896454811096</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6160766030030931</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.358894051676196</v>
+        <v>4.989783734595646</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.1200191751122475</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.358895142922653</v>
+        <v>4.989784825842103</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.1127012446522713</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.358894453315517</v>
+        <v>4.989784136234967</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.115323431789875</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.358894483627919</v>
+        <v>4.989784166547369</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.03618448972702026</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6160766030030931</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.358894294175409</v>
+        <v>4.989783977094859</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01939019188284874</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.04456170319311462</v>
+        <v>-0.3</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.358894347222112</v>
+        <v>4.989784030141562</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.07208926975727081</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.358894400268814</v>
+        <v>4.989784083188264</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.07449248433113098</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.358894362378312</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.07258128374814987</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.358894233550605</v>
+        <v>4.989783916470055</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.07464562356472015</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.358894089566698</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.07756999135017395</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.35889393042659</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.07262192666530609</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.358893983473293</v>
+        <v>4.989783666392743</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.07246661931276321</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.35889393042659</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.07766098529100418</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.35889393042659</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.07848053425550461</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.358893748552181</v>
+        <v>4.989783431471631</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.06964530795812607</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.358893915270389</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.07698062062263489</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.358894112300999</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.07588011771440506</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.358893953160891</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.07814013957977295</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.358893991051393</v>
+        <v>4.989783673970843</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05240761116147041</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.358894188082003</v>
+        <v>4.989783871001453</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.07670792937278748</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.358894165347702</v>
+        <v>4.989783848267152</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.07368941605091095</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.358894013785694</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.06972844898700714</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.35889393800469</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.08107569068670273</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.358894036519996</v>
+        <v>4.989783719439446</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.06404536962509155</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.358894044098096</v>
+        <v>4.989783727017546</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.07208111882209778</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.35889430933161</v>
+        <v>4.98978399225106</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.08273430168628693</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.358894013785694</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06134289503097534</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.358894256284906</v>
+        <v>4.989783939204357</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.09584866464138031</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.358894339644011</v>
+        <v>4.989784022563462</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03949128463864326</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.358894172925803</v>
+        <v>4.989783855845253</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.03356979414820671</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.358894362378312</v>
+        <v>4.989784045297762</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.06543619930744171</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.358894013785694</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.07390286773443222</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.358893809176983</v>
+        <v>4.989783492096433</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.06898682564496994</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.358893922848489</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.07293159514665604</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.35889393800469</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.07664234936237335</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.358893703083579</v>
+        <v>4.989783386003029</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.06802935898303986</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.358893763708381</v>
+        <v>4.989783446627831</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.07509878277778625</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.358893634880674</v>
+        <v>4.989783317800124</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.04876025021076202</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.358893771286482</v>
+        <v>4.989783454205933</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0821068063378334</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.35889394558279</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.07000958919525146</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.358894089566698</v>
+        <v>4.989783772486148</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.07417763769626617</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.358893922848489</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.07385562360286713</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.358893915270389</v>
+        <v>4.989783598189839</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06672617793083191</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.358893627302574</v>
+        <v>4.989783310222024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.05578489974141121</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.358893642458775</v>
+        <v>4.989783325378225</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.06056725978851318</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.358893869801787</v>
+        <v>4.989783552721237</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.06509028375148773</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.358893854645586</v>
+        <v>4.989783537565036</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.06133585423231125</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.358893960738992</v>
+        <v>4.989783643658441</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.05474111437797546</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.358893687927377</v>
+        <v>4.989783370846827</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.05759956687688828</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.358893786442682</v>
+        <v>4.989783469362132</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.06024985760450363</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.35889393800469</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.06120387464761734</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.358893953160891</v>
+        <v>4.989783636080341</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.06549876928329468</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.35889393042659</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.06641718000173569</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.358894013785694</v>
+        <v>4.989783696705144</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0612739771604538</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.358894112300999</v>
+        <v>4.98978379522045</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.05671405792236328</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.35889394558279</v>
+        <v>4.989783628502241</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.05940168350934982</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.35889393042659</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.06236868351697922</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.358893900114188</v>
+        <v>4.989783583033638</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.06222761794924736</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.358893884957988</v>
+        <v>4.989783567877438</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.06086735427379608</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.358893922848489</v>
+        <v>4.989783605767939</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0702192634344101</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.35889393800469</v>
+        <v>4.989783620924141</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.09730133414268494</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.35889393042659</v>
+        <v>4.98978361334604</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_5_000007.xlsx
+++ b/out/Attention-mamba2_repeat_5_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.2022098004817963</v>
+        <v>-0.2022096514701843</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1644747257232666</v>
+        <v>-0.1644745469093323</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1431114673614502</v>
+        <v>-0.143111377954483</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.2115134596824646</v>
+        <v>-0.2115131318569183</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.2847812175750732</v>
+        <v>-0.2847810387611389</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.2380796074867249</v>
+        <v>-0.2380794584751129</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.2111549079418182</v>
+        <v>-0.2111548781394958</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2362108528614044</v>
+        <v>-0.2362107336521149</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2208275198936462</v>
+        <v>-0.2208274006843567</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.2269338369369507</v>
+        <v>-0.2269337177276611</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.2165277302265167</v>
+        <v>-0.2165276408195496</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.2107262015342712</v>
+        <v>-0.2107260823249817</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.2270304560661316</v>
+        <v>-0.2270303070545197</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2268794178962708</v>
+        <v>-0.2268793880939484</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.2599999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.2436006665229797</v>
+        <v>-0.2436005473136902</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.2202641367912292</v>
+        <v>-0.2202641069889069</v>
       </c>
       <c r="JB17" t="n">
         <v>0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2206695973873138</v>
+        <v>-0.2206694483757019</v>
       </c>
       <c r="JB18" t="n">
         <v>0.02000000000000007</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.2150301933288574</v>
+        <v>-0.2150300741195679</v>
       </c>
       <c r="JB19" t="n">
         <v>0.02000000000000007</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.2331482172012329</v>
+        <v>-0.2331480383872986</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.1199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.2258205711841583</v>
+        <v>-0.225820392370224</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.2599999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.2503321468830109</v>
+        <v>-0.2503320574760437</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2713155448436737</v>
+        <v>-0.2713155150413513</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.25316521525383</v>
+        <v>-0.253165066242218</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2328386902809143</v>
+        <v>-0.2328385710716248</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2221862375736237</v>
+        <v>-0.2221859991550446</v>
       </c>
       <c r="JB26" t="n">
         <v>0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2179197072982788</v>
+        <v>-0.2179196178913116</v>
       </c>
       <c r="JB27" t="n">
         <v>0.16</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2128949761390686</v>
+        <v>-0.2128948867321014</v>
       </c>
       <c r="JB28" t="n">
         <v>0.1600000000000001</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.2417771816253662</v>
+        <v>-0.2417771518230438</v>
       </c>
       <c r="JB29" t="n">
         <v>0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2391280233860016</v>
+        <v>-0.2391279637813568</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2300002872943878</v>
+        <v>-0.2300001382827759</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.2148258090019226</v>
+        <v>-0.2148256599903107</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2269738018512726</v>
+        <v>-0.2269737422466278</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.2244530618190765</v>
+        <v>-0.2244529128074646</v>
       </c>
       <c r="JB34" t="n">
         <v>0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.2349183559417725</v>
+        <v>-0.2349182963371277</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3079775273799896</v>
+        <v>-0.3079773783683777</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.09377837926149368</v>
+        <v>-0.09377828985452652</v>
       </c>
       <c r="JB37" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0452384427189827</v>
+        <v>-0.04523835331201553</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.0128650888800621</v>
+        <v>0.01286525279283524</v>
       </c>
       <c r="JB39" t="n">
         <v>0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.01095288991928101</v>
+        <v>0.01095297932624817</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.02926206588745117</v>
+        <v>0.02926205843687057</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.03131918609142303</v>
+        <v>0.03131913393735886</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.05926530435681343</v>
+        <v>0.0592653900384903</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.009758524596691132</v>
+        <v>0.00975838303565979</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.02000000000000007</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.02585101127624512</v>
+        <v>-0.02585116773843765</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.16</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.03266854584217072</v>
+        <v>-0.0326685756444931</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0105474665760994</v>
+        <v>-0.01054748147726059</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.01222645491361618</v>
+        <v>-0.01222661882638931</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.16</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.002193674445152283</v>
+        <v>0.002193614840507507</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.02000000000000007</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.02357619628310204</v>
+        <v>0.02357611805200577</v>
       </c>
       <c r="JB50" t="n">
         <v>0.1199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.08561885356903076</v>
+        <v>0.08561865985393524</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.05944843590259552</v>
+        <v>0.05944859236478806</v>
       </c>
       <c r="JB52" t="n">
         <v>0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.05609896406531334</v>
+        <v>0.05609879270195961</v>
       </c>
       <c r="JB53" t="n">
         <v>0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.08212609589099884</v>
+        <v>0.08212603628635406</v>
       </c>
       <c r="JB54" t="n">
         <v>0.8599999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.08625451475381851</v>
+        <v>0.08625444769859314</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.07147236913442612</v>
+        <v>0.07147228717803955</v>
       </c>
       <c r="JB56" t="n">
         <v>0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.106353834271431</v>
+        <v>0.106353871524334</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.02000000000000007</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.02984552830457687</v>
+        <v>0.02984543889760971</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.16</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.04234930872917175</v>
+        <v>-0.04234949499368668</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.02000000000000007</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.05573703348636627</v>
+        <v>0.05573682487010956</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.16</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.07937610149383545</v>
+        <v>0.07937610894441605</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.02000000000000007</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.06973107159137726</v>
+        <v>0.06973106414079666</v>
       </c>
       <c r="JB62" t="n">
         <v>0.1199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.07617244124412537</v>
+        <v>0.07617245614528656</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.05462924018502235</v>
+        <v>0.05462917312979698</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.02949896454811096</v>
+        <v>-0.02949913591146469</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.1200191751122475</v>
+        <v>-0.1200192794203758</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.1127012446522713</v>
+        <v>-0.1127014681696892</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.115323431789875</v>
+        <v>-0.1153232827782631</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.8599999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.03618448972702026</v>
+        <v>-0.03618449717760086</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.5799999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.01939019188284874</v>
+        <v>0.01939013227820396</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.3</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.07208926975727081</v>
+        <v>0.0720892995595932</v>
       </c>
       <c r="JB71" t="n">
         <v>0.5799999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.07449248433113098</v>
+        <v>0.07449249178171158</v>
       </c>
       <c r="JB72" t="n">
         <v>0.8599999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.07258128374814987</v>
+        <v>0.07258127629756927</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.07464562356472015</v>
+        <v>0.07464569061994553</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.07756999135017395</v>
+        <v>0.07757001370191574</v>
       </c>
       <c r="JB75" t="n">
         <v>0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.07262192666530609</v>
+        <v>0.07262188941240311</v>
       </c>
       <c r="JB76" t="n">
         <v>0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.07246661931276321</v>
+        <v>0.07246669381856918</v>
       </c>
       <c r="JB77" t="n">
         <v>0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.07766098529100418</v>
+        <v>0.0776609480381012</v>
       </c>
       <c r="JB78" t="n">
         <v>0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.07848053425550461</v>
+        <v>0.07848049700260162</v>
       </c>
       <c r="JB79" t="n">
         <v>0.1199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.06964530795812607</v>
+        <v>0.06964527070522308</v>
       </c>
       <c r="JB80" t="n">
         <v>0.2599999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.07698062062263489</v>
+        <v>0.07698066532611847</v>
       </c>
       <c r="JB81" t="n">
         <v>0.2599999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.07588011771440506</v>
+        <v>0.07588003575801849</v>
       </c>
       <c r="JB82" t="n">
         <v>0.1199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.07814013957977295</v>
+        <v>0.07814007997512817</v>
       </c>
       <c r="JB83" t="n">
         <v>0.2599999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.05240761116147041</v>
+        <v>0.05240750312805176</v>
       </c>
       <c r="JB84" t="n">
         <v>0.1199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.07670792937278748</v>
+        <v>0.07670789211988449</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.07368941605091095</v>
+        <v>0.07368938624858856</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.02000000000000007</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.06972844898700714</v>
+        <v>0.06972841918468475</v>
       </c>
       <c r="JB87" t="n">
         <v>0.1199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.08107569068670273</v>
+        <v>0.08107565343379974</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.02000000000000007</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.06404536962509155</v>
+        <v>0.0640452578663826</v>
       </c>
       <c r="JB89" t="n">
         <v>0.1199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.07208111882209778</v>
+        <v>0.072081059217453</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1199999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.08273430168628693</v>
+        <v>0.08273425698280334</v>
       </c>
       <c r="JB91" t="n">
         <v>0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06134289503097534</v>
+        <v>0.061342753469944</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.02000000000000007</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.09584866464138031</v>
+        <v>0.09584861993789673</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.03949128463864326</v>
+        <v>0.03949121385812759</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.03356979414820671</v>
+        <v>0.03356973081827164</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.1600000000000001</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.06543619930744171</v>
+        <v>0.06543611735105515</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.07390286773443222</v>
+        <v>0.07390284538269043</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.3</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.06898682564496994</v>
+        <v>0.06898683309555054</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.16</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.07293159514665604</v>
+        <v>0.07293157279491425</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.07664234936237335</v>
+        <v>0.07664231956005096</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.06802935898303986</v>
+        <v>0.06802929937839508</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.07509878277778625</v>
+        <v>0.07509873062372208</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.04876025021076202</v>
+        <v>0.04876032099127769</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0821068063378334</v>
+        <v>0.08210667222738266</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.07000958919525146</v>
+        <v>0.07000952214002609</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.07417763769626617</v>
+        <v>0.07417754828929901</v>
       </c>
       <c r="JB106" t="n">
         <v>0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.07385562360286713</v>
+        <v>0.07385547459125519</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06672617793083191</v>
+        <v>0.06672641634941101</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.05578489974141121</v>
+        <v>0.05578488484025002</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.06056725978851318</v>
+        <v>0.06056729704141617</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.06509028375148773</v>
+        <v>0.06509023159742355</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.06133585423231125</v>
+        <v>0.06133584678173065</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.05474111437797546</v>
+        <v>0.05474117770791054</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.05759956687688828</v>
+        <v>0.0575995147228241</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.06024985760450363</v>
+        <v>0.06024976074695587</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.7199999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.06120387464761734</v>
+        <v>0.06120389699935913</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.5799999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.06549876928329468</v>
+        <v>0.0654987096786499</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.06641718000173569</v>
+        <v>0.06641721725463867</v>
       </c>
       <c r="JB118" t="n">
         <v>0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.0612739771604538</v>
+        <v>0.06127386540174484</v>
       </c>
       <c r="JB119" t="n">
         <v>0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.05671405792236328</v>
+        <v>0.05671394988894463</v>
       </c>
       <c r="JB120" t="n">
         <v>0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.05940168350934982</v>
+        <v>0.05940166860818863</v>
       </c>
       <c r="JB121" t="n">
         <v>0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.06236868351697922</v>
+        <v>0.0623687170445919</v>
       </c>
       <c r="JB122" t="n">
         <v>0.16</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.06222761794924736</v>
+        <v>0.06222747266292572</v>
       </c>
       <c r="JB123" t="n">
         <v>0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.06086735427379608</v>
+        <v>0.06086713075637817</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.0702192634344101</v>
+        <v>0.07021919637918472</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5800000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.09730133414268494</v>
+        <v>0.09730140864849091</v>
       </c>
       <c r="JB126" t="n">
         <v>0.72</v>
